--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT JUNTA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT JUNTA.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JG JUNTA VALFLEX FAZER150 2014/ CROSSER XTZ150 2014/ FACTOR150 2016 57016</t>
+          <t>JOGO JUNTA VALFLEX FAZER150 2014/ CROSSER XTZ150 2014/ FACTOR150 2016 57016</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JG JUNTA VALFLEX TITAN FAN CG150/ BROS NXR150 2006 56256E</t>
+          <t>JOGO JUNTA VALFLEX TITAN FAN CG150/ BROS NXR150 2006 56256E</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX CB300/ XRE300 5986885009</t>
+          <t>JOGO JUNTA W-MAX CB300/ XRE300 5986885009</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS SUSUKI YES125 2005 A 2007</t>
+          <t>JOGO JUNTA VEDAMOTOS SUSUKI YES125 2005 A 2007</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JG JUNTA VEDAMOTOS BROS NXR160/ FAN TITAN160 </t>
+          <t xml:space="preserve">JOGO JUNTA VEDAMOTOS BROS NXR160/ FAN TITAN160 </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS CG TODAY TITAN 1999</t>
+          <t>JOGO JUNTA VEDAMOTOS CG TODAY TITAN 1999</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS FAN CG125 2009</t>
+          <t>JOGO JUNTA VEDAMOTOS FAN CG125 2009</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS YS250 FAZER/ LANDER XTZ250/ TENERÉ 250</t>
+          <t>JOGO JUNTA VEDAMOTOS YS250 FAZER/ LANDER XTZ250/ TENERÉ 250</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS CB300/ XRE300</t>
+          <t>JOGO JUNTA VEDAMOTOS CB300/ XRE300</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS CG TITAN150/ FAN 2004/ CRF 150F/ BROS NXR150 2006</t>
+          <t>JOGO JUNTA VEDAMOTOS CG TITAN150/ FAN 2004/ CRF 150F/ BROS NXR150 2006</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS YS FAZER CROSSER XTZ150 2014/ FACTOR150 2016/ FAZER150 2023</t>
+          <t>JOGO JUNTA VEDAMOTOS YS FAZER CROSSER XTZ150 2014/ FACTOR150 2016/ FAZER150 2023</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
+          <t>JOGO JUNTA VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS POP100 2006 A 2015</t>
+          <t>JOGO JUNTA VEDAMOTOS POP100 2006 A 2015</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JG JUNTA VEDAMOTOS BIZ125 </t>
+          <t xml:space="preserve">JOGO JUNTA VEDAMOTOS BIZ125 </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS BIZ C100 1998 A 2005 DREAM/ BIZ KS/ WEB100</t>
+          <t>JOGO JUNTA VEDAMOTOS BIZ C100 1998 A 2005 DREAM/ BIZ KS/ WEB100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS POP110I 2015/ BIZ110I 2016</t>
+          <t>JOGO JUNTA VEDAMOTOS POP110I 2015/ BIZ110I 2016</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX SUSUKI YES125 2008 5986885013</t>
+          <t>JOGO JUNTA W-MAX SUSUKI YES125 2008 5986885013</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX FAZER150/ CROSSER XTZ150 5986885011</t>
+          <t>JOGO JUNTA W-MAX FAZER150/ CROSSER XTZ150 5986885011</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JG JUNTA MHX YBR125 2000 A 2008/ CACTOR125 2009 A 2018</t>
+          <t>JOGO JUNTA MHX YBR125 2000 A 2008/ CACTOR125 2009 A 2018</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS YBR XTZ125</t>
+          <t>JOGO JUNTA VEDAMOTOS YBR XTZ125</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS CG FAN TITAN 2000 KS/ BROS NXR125</t>
+          <t>JOGO JUNTA VEDAMOTOS CG FAN TITAN 2000 KS/ BROS NXR125</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JG JUNTA GEAP BIZ110 POP110 2010</t>
+          <t>JOGO JUNTA GEAP BIZ110 POP110 2010</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX CG FAN TITAN150 2004 A 2015 5986885006</t>
+          <t>JOGO JUNTA W-MAX CG FAN TITAN150 2004 A 2015 5986885006</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX BIZ125 5986885001</t>
+          <t>JOGO JUNTA W-MAX BIZ125 5986885001</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS CB250 TWISTER 2016</t>
+          <t>JOGO JUNTA VEDAMOTOS CB250 TWISTER 2016</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX TWISTER CBX250/ TORNADO XR250 5986885008</t>
+          <t>JOGO JUNTA W-MAX TWISTER CBX250/ TORNADO XR250 5986885008</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JG JUNTA VEDAMOTOS SUSUKI GSR150I</t>
+          <t>JOGO JUNTA VEDAMOTOS SUSUKI GSR150I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JG JUNTA W-MAX BIZ100/ WEB100/ PP100 5986885002</t>
+          <t>JOGO JUNTA W-MAX BIZ100/ WEB100/ PP100 5986885002</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP TWISTER CBX250/ TORNADO XR250 110412</t>
+          <t>JOGO JUNTA KMP TWISTER CBX250/ TORNADO XR250 110412</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP CG125 FAN TITAN 1104008</t>
+          <t>JOGO JUNTA KMP CG125 FAN TITAN 1104008</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP TITAN FAN CG160 1104592</t>
+          <t>JOGO JUNTA KMP TITAN FAN CG160 1104592</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP CB300/ XRE300 1104002</t>
+          <t>JOGO JUNTA KMP CB300/ XRE300 1104002</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP FAN CG125 2009 1104020</t>
+          <t>JOGO JUNTA KMP FAN CG125 2009 1104020</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP TITAN FAN CG150 1104007</t>
+          <t>JOGO JUNTA KMP TITAN FAN CG150 1104007</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JG JUNTA KMP BIZ110 1105249</t>
+          <t>JOGO JUNTA KMP BIZ110 1105249</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT JUNTA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT JUNTA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,11 +532,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,11 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,11 +572,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -616,11 +592,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,11 +612,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -666,11 +632,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -691,7 +652,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -712,11 +672,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,7 +692,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -758,11 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +732,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -808,11 +752,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,7 +772,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -854,7 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -875,11 +812,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -900,11 +832,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -925,7 +852,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -946,7 +872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -967,7 +892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -988,7 +912,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,7 +932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1030,7 +952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1051,11 +972,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1076,11 +992,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1101,7 +1012,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1122,7 +1032,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1143,7 +1052,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1164,7 +1072,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,7 +1092,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1206,7 +1112,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1227,7 +1132,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
